--- a/Topological Sorting/活頁簿1.xlsx
+++ b/Topological Sorting/活頁簿1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\C語言\C-Learning\Topological Sorting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9457480-8F96-41CD-8961-B03F7520BA25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7BE806-A58D-43DF-9CE8-1A70C02AC107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BCCA6945-B14D-4DC1-B7C0-C413FB35E78C}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="18">
   <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -75,6 +75,39 @@
   </si>
   <si>
     <t>I</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>起床</t>
+  </si>
+  <si>
+    <t>刷牙</t>
+  </si>
+  <si>
+    <t>洗臉</t>
+  </si>
+  <si>
+    <t>穿衣</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>發動汽車</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打開音響</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>吃早餐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打領帶</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>開車上班</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -138,14 +171,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -461,205 +494,413 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{507FEE79-EC0E-4548-9513-55194F1C711B}">
-  <dimension ref="B1:K36"/>
+  <dimension ref="B1:N36"/>
   <sheetFormatPr defaultColWidth="6.5546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="2.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="2.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="2.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="2.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="2.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="2.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="28" width="3.88671875" style="1" customWidth="1"/>
-    <col min="29" max="16384" width="6.5546875" style="1"/>
+    <col min="1" max="1" width="3.88671875" style="2" customWidth="1"/>
+    <col min="2" max="14" width="5" style="2" customWidth="1"/>
+    <col min="15" max="28" width="3.88671875" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="6.5546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="2"/>
-      <c r="C4" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="2" t="s">
+    <row r="1" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
+    <row r="5" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" s="1">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1">
+        <v>0</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
+    <row r="6" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>0</v>
+      </c>
+      <c r="D6" s="1">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1">
+        <v>1</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
+      <c r="C7" s="1">
+        <v>0</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1">
+        <v>1</v>
+      </c>
+      <c r="G7" s="1">
+        <v>0</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="8" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="2" t="s">
+    <row r="8" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
+      <c r="C8" s="1">
+        <v>0</v>
+      </c>
+      <c r="D8" s="1">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="9" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
+      <c r="C9" s="1">
+        <v>0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1">
+        <v>0</v>
+      </c>
+      <c r="H9" s="1">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1">
+        <v>1</v>
+      </c>
+      <c r="J9" s="1">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="10" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="2" t="s">
+    <row r="10" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
+      <c r="C10" s="1">
+        <v>0</v>
+      </c>
+      <c r="D10" s="1">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="11" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="2" t="s">
+    <row r="11" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
+      <c r="C11" s="1">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
+      <c r="G11" s="1">
+        <v>0</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="12" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="2" t="s">
+    <row r="12" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
+      <c r="C12" s="1">
+        <v>0</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1">
+        <v>0</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="13" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
+      <c r="C13" s="1">
+        <v>0</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1">
+        <v>0</v>
+      </c>
+      <c r="K13" s="1">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="14" spans="2:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="2:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="2:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" s="1" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Topological Sorting/活頁簿1.xlsx
+++ b/Topological Sorting/活頁簿1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\C語言\C-Learning\Topological Sorting\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A7BE806-A58D-43DF-9CE8-1A70C02AC107}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E6F006D-A80F-4A88-BD5E-B439085D5194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BCCA6945-B14D-4DC1-B7C0-C413FB35E78C}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{BCCA6945-B14D-4DC1-B7C0-C413FB35E78C}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -495,18 +495,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{507FEE79-EC0E-4548-9513-55194F1C711B}">
   <dimension ref="B1:N36"/>
-  <sheetFormatPr defaultColWidth="6.5546875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.58203125" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="3.9140625" style="2" customWidth="1"/>
     <col min="2" max="14" width="5" style="2" customWidth="1"/>
-    <col min="15" max="28" width="3.88671875" style="2" customWidth="1"/>
-    <col min="29" max="16384" width="6.5546875" style="2"/>
+    <col min="15" max="28" width="3.9140625" style="2" customWidth="1"/>
+    <col min="29" max="16384" width="6.58203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="4" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
         <v>0</v>
@@ -536,7 +536,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
@@ -574,7 +574,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
@@ -612,7 +612,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="1" t="s">
         <v>2</v>
       </c>
@@ -650,7 +650,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="1" t="s">
         <v>3</v>
       </c>
@@ -688,7 +688,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="1" t="s">
         <v>4</v>
       </c>
@@ -726,7 +726,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
@@ -764,7 +764,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
@@ -802,7 +802,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
@@ -840,7 +840,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
@@ -878,29 +878,57 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="15" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="16" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="33" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="34" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="35" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="36" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="2:14" ht="30" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="15" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="2">
+        <v>0</v>
+      </c>
+      <c r="D15" s="2">
+        <v>1</v>
+      </c>
+      <c r="E15" s="2">
+        <v>1</v>
+      </c>
+      <c r="F15" s="2">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" s="2">
+        <v>2</v>
+      </c>
+      <c r="K15" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="17" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="18" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="19" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="20" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="22" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="23" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="25" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="26" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="27" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="28" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="29" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="30" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="31" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="32" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="33" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="34" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="35" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="36" s="2" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
